--- a/examples/TAURI_REWRITE/EXCEL/KeyTable.xlsx
+++ b/examples/TAURI_REWRITE/EXCEL/KeyTable.xlsx
@@ -9,13 +9,14 @@
     <sheet sheetId="3" name="GroupTarget" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="NoKeyTarget" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="_DropDown" state="veryHidden" r:id="rId8"/>
+    <sheet sheetId="6" name="_DataManager" state="veryHidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -39,6 +40,12 @@
   </si>
   <si>
     <t>FixtureState_ACTIVE</t>
+  </si>
+  <si>
+    <t>DataManager.ExcelMetadata</t>
+  </si>
+  <si>
+    <t>{"magic":"DataManager.ExcelMetadata","version":1,"sourceFile":"KeyTable.proto","fingerprint":"dm1-98e4d920","tables":[{"messageName":"SingleTarget","memoColumns":[]},{"messageName":"CompositeTarget","memoColumns":[]},{"messageName":"GroupTarget","memoColumns":[]},{"messageName":"NoKeyTarget","memoColumns":[]}]}</t>
   </si>
 </sst>
 </file>
@@ -565,4 +572,28 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>